--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487124_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487124_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.3514</v>
+        <v>8.162000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>7.4837</v>
+        <v>7.0802</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8677</v>
+        <v>1.0818</v>
       </c>
       <c r="G2" t="n">
         <v>5.7035</v>
@@ -610,13 +610,13 @@
         <v>1.3511</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2691</v>
+        <v>1.0797</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3326</v>
+        <v>0.929</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0635</v>
+        <v>0.1507</v>
       </c>
       <c r="V2" t="n">
         <v>1.1857</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5776</v>
+        <v>4.3301</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3363</v>
+        <v>2.8747</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2413</v>
+        <v>1.4554</v>
       </c>
       <c r="G3" t="n">
         <v>2.7407</v>
@@ -688,13 +688,13 @@
         <v>1.7371</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1401</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1904</v>
+        <v>0.7288</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3305</v>
+        <v>-0.1164</v>
       </c>
       <c r="V3" t="n">
         <v>1.5561</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4254</v>
+        <v>0.5721000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>4.2711</v>
+        <v>4.4714</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.8457</v>
+        <v>-3.8993</v>
       </c>
       <c r="G4" t="n">
         <v>1.8601</v>
@@ -766,13 +766,13 @@
         <v>0.579</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2023</v>
+        <v>0.349</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4164</v>
+        <v>-0.2161</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6187</v>
+        <v>0.5651</v>
       </c>
       <c r="V4" t="n">
         <v>-0.2859</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3599</v>
+        <v>-0.5067</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4037</v>
+        <v>0.2034</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7635999999999999</v>
+        <v>-0.7101</v>
       </c>
       <c r="G5" t="n">
         <v>-0.4247</v>
@@ -844,13 +844,13 @@
         <v>0.772</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4508</v>
+        <v>0.3041</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3847</v>
+        <v>0.1844</v>
       </c>
       <c r="U5" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.1196</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7271</v>
+        <v>-0.5278</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1159</v>
+        <v>0.2441</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6112</v>
+        <v>-0.7718</v>
       </c>
       <c r="G6" t="n">
         <v>0.0288</v>
@@ -922,13 +922,13 @@
         <v>0.386</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2842</v>
+        <v>-0.0849</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.238</v>
+        <v>0.122</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0463</v>
+        <v>-0.2069</v>
       </c>
       <c r="V6" t="n">
         <v>-0.8576</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2654</v>
+        <v>-0.6586</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6868</v>
+        <v>-1.2674</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4215</v>
+        <v>0.6089</v>
       </c>
       <c r="G7" t="n">
         <v>-0.6937</v>
@@ -1000,13 +1000,13 @@
         <v>1.158</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4211</v>
+        <v>1.0278</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3993</v>
+        <v>0.8187</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0218</v>
+        <v>0.2092</v>
       </c>
       <c r="V7" t="n">
         <v>-1.1857</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. KARATZAS LACABEX</t>
+          <t>G. RUIZ ALCALA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6805</v>
+        <v>-1.6513</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.1155</v>
+        <v>-2.5543</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4351</v>
+        <v>0.903</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.8872</v>
+        <v>-2.4267</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.3382</v>
+        <v>-1.834</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5491</v>
+        <v>-0.5926</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7128</v>
+        <v>-2.5269</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.59</v>
+        <v>-1.9407</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1228</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1744</v>
+        <v>0.1002</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7481</v>
+        <v>0.1067</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4263</v>
+        <v>-0.0064</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.158</v>
+        <v>0.579</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.3161</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.158</v>
+        <v>0.579</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1368</v>
+        <v>0.1963</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3146</v>
+        <v>-0.0274</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4514</v>
+        <v>0.2237</v>
       </c>
       <c r="V8" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. RUIZ ALCALA</t>
+          <t>A. KARATZAS LACABEX</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.691</v>
+        <v>-1.8431</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5137</v>
+        <v>-2.0372</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8227</v>
+        <v>0.1941</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.4267</v>
+        <v>-1.8872</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.834</v>
+        <v>-1.3382</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5926</v>
+        <v>-0.5491</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.5269</v>
+        <v>-0.7128</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.9407</v>
+        <v>-0.59</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5862000000000001</v>
+        <v>-0.1228</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1002</v>
+        <v>-1.1744</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1067</v>
+        <v>-0.7481</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0064</v>
+        <v>-0.4263</v>
       </c>
       <c r="P9" t="n">
-        <v>0.579</v>
+        <v>-1.158</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.3161</v>
       </c>
       <c r="R9" t="n">
-        <v>0.579</v>
+        <v>1.158</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1567</v>
+        <v>-0.0258</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0132</v>
+        <v>-0.2363</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1434</v>
+        <v>0.2105</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1774</v>
+        <v>-2.5343</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1512</v>
+        <v>-3.4546</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9738</v>
+        <v>0.9203</v>
       </c>
       <c r="G10" t="n">
         <v>-1.4435</v>
@@ -1234,13 +1234,13 @@
         <v>1.5441</v>
       </c>
       <c r="S10" t="n">
-        <v>1.359</v>
+        <v>1.0021</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9162</v>
+        <v>0.6128</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4428</v>
+        <v>0.3893</v>
       </c>
       <c r="V10" t="n">
         <v>-1.5138</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.3733</v>
+        <v>-4.3098</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.1361</v>
+        <v>-3.6979</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2372</v>
+        <v>-0.612</v>
       </c>
       <c r="G11" t="n">
         <v>-1.7574</v>
@@ -1312,13 +1312,13 @@
         <v>1.3511</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8051</v>
+        <v>0.8685</v>
       </c>
       <c r="T11" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.5097</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7337</v>
+        <v>0.3589</v>
       </c>
       <c r="V11" t="n">
         <v>-2.4559</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-10.5504</v>
+        <v>-10.016</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.072699999999999</v>
+        <v>-7.6721</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.4777</v>
+        <v>-2.3439</v>
       </c>
       <c r="G12" t="n">
         <v>-3.373</v>
@@ -1390,13 +1390,13 @@
         <v>0.965</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6683</v>
+        <v>-0.1338</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5803</v>
+        <v>-0.1798</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.08790000000000001</v>
+        <v>0.0459</v>
       </c>
       <c r="V12" t="n">
         <v>-2.4559</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.4706</v>
+        <v>-8.9834</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.297099999999999</v>
+        <v>-5.809699999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.1733</v>
+        <v>-3.1736</v>
       </c>
       <c r="G13" t="n">
         <v>-1.673100000000001</v>
@@ -1468,13 +1468,13 @@
         <v>11.5804</v>
       </c>
       <c r="S13" t="n">
-        <v>3.7083</v>
+        <v>5.195400000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>1.7585</v>
+        <v>3.2458</v>
       </c>
       <c r="U13" t="n">
-        <v>1.9497</v>
+        <v>1.9496</v>
       </c>
       <c r="V13" t="n">
         <v>-4.785</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.9172</v>
+        <v>8.6248</v>
       </c>
       <c r="E14" t="n">
-        <v>4.3023</v>
+        <v>4.5026</v>
       </c>
       <c r="F14" t="n">
-        <v>3.6149</v>
+        <v>4.1222</v>
       </c>
       <c r="G14" t="n">
         <v>3.3981</v>
@@ -1546,13 +1546,13 @@
         <v>3.6672</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.967</v>
+        <v>-0.2594</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5975</v>
+        <v>-0.3972</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3695</v>
+        <v>0.1378</v>
       </c>
       <c r="V14" t="n">
         <v>2.784</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.1943</v>
+        <v>7.3702</v>
       </c>
       <c r="E15" t="n">
-        <v>3.6219</v>
+        <v>4.0225</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5724</v>
+        <v>3.3478</v>
       </c>
       <c r="G15" t="n">
         <v>3.1229</v>
@@ -1624,13 +1624,13 @@
         <v>3.0881</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8937</v>
+        <v>0.2822</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6107</v>
+        <v>-0.2102</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2829</v>
+        <v>0.4924</v>
       </c>
       <c r="V15" t="n">
         <v>1.842</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.8856</v>
+        <v>3.8594</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1081</v>
+        <v>1.307</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7775</v>
+        <v>2.5525</v>
       </c>
       <c r="G16" t="n">
         <v>-0.2446</v>
@@ -1702,13 +1702,13 @@
         <v>3.4741</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0482</v>
+        <v>-0.07439999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7377</v>
+        <v>-0.0634</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.786</v>
+        <v>-0.011</v>
       </c>
       <c r="V16" t="n">
         <v>3.5994</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.3514</v>
+        <v>3.3977</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0626</v>
+        <v>0.1627</v>
       </c>
       <c r="F17" t="n">
-        <v>3.2888</v>
+        <v>3.235</v>
       </c>
       <c r="G17" t="n">
         <v>0.374</v>
@@ -1780,13 +1780,13 @@
         <v>2.7021</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6035</v>
+        <v>0.6497000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0621</v>
+        <v>0.038</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6656</v>
+        <v>0.6117</v>
       </c>
       <c r="V17" t="n">
         <v>-0.3281</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.3853</v>
+        <v>2.6656</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9746</v>
+        <v>1.7743</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4107</v>
+        <v>0.8913</v>
       </c>
       <c r="G18" t="n">
         <v>2.8089</v>
@@ -1858,13 +1858,13 @@
         <v>2.7021</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5394</v>
+        <v>-0.2591</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1361</v>
+        <v>-0.3364</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4032</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="V18" t="n">
         <v>-0.6562</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3745</v>
+        <v>-0.5886</v>
       </c>
       <c r="E19" t="n">
         <v>-0.7321</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3577</v>
+        <v>0.1435</v>
       </c>
       <c r="G19" t="n">
         <v>0.0049</v>
@@ -1936,13 +1936,13 @@
         <v>0.386</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1996</v>
+        <v>-0.0145</v>
       </c>
       <c r="T19" t="n">
         <v>-0.119</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3186</v>
+        <v>0.1044</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.962</v>
+        <v>-2.2425</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.375</v>
+        <v>-0.5753</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5869</v>
+        <v>-1.6673</v>
       </c>
       <c r="G20" t="n">
         <v>-1.66</v>
@@ -2014,13 +2014,13 @@
         <v>0.772</v>
       </c>
       <c r="S20" t="n">
-        <v>0.154</v>
+        <v>-0.1266</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2512</v>
+        <v>0.0509</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.09719999999999999</v>
+        <v>-0.1775</v>
       </c>
       <c r="V20" t="n">
         <v>-1.228</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.9629</v>
+        <v>-3.3888</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.3824</v>
+        <v>-4.1821</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4195</v>
+        <v>0.7933</v>
       </c>
       <c r="G21" t="n">
         <v>-2.0715</v>
@@ -2092,13 +2092,13 @@
         <v>1.5441</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2195</v>
+        <v>-0.6455</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6544</v>
+        <v>-0.4541</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5652</v>
+        <v>-0.1914</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2859</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.9641</v>
+        <v>-6.5569</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.4065</v>
+        <v>-3.1061</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.5576</v>
+        <v>-3.4508</v>
       </c>
       <c r="G22" t="n">
         <v>-4.0595</v>
@@ -2170,13 +2170,13 @@
         <v>0.965</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9974</v>
+        <v>-0.5903</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7588</v>
+        <v>-0.4584</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2386</v>
+        <v>-0.1319</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9421</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>10.4703</v>
+        <v>13.1409</v>
       </c>
       <c r="E23" t="n">
         <v>3.173499999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>7.297000000000001</v>
+        <v>9.967500000000001</v>
       </c>
       <c r="G23" t="n">
         <v>1.673200000000001</v>
@@ -2248,13 +2248,13 @@
         <v>19.3007</v>
       </c>
       <c r="S23" t="n">
-        <v>-3.7081</v>
+        <v>-1.0379</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.9497</v>
+        <v>-1.9498</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.7584</v>
+        <v>0.9118000000000001</v>
       </c>
       <c r="V23" t="n">
         <v>4.7851</v>
